--- a/VALIDATION/param_shift_summary.xlsx
+++ b/VALIDATION/param_shift_summary.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://conchaytoro365-my.sharepoint.com/personal/cristobal_torrealba_conchaytoro_cl/Documents/Documentos/Doctorado/Artículos/Artículo - Estimación/Codes/VALIDATION/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_8EA8403B1030921FD2FE31D2F8F2D3C2F4D4A125" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C733A883-C9A0-4055-B30F-EDC9E9409C4D}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -92,8 +73,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,21 +137,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -208,7 +181,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -242,7 +215,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -277,10 +249,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -453,11 +424,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,7 +445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -482,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>0.20507403814592981</v>
+        <v>0.2050740381459298</v>
       </c>
       <c r="D2">
-        <v>0.27860078506594271</v>
+        <v>0.2786007850659427</v>
       </c>
       <c r="E2">
-        <v>0.35853756811328569</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.3585375681132857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -499,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>0.76330822264540721</v>
+        <v>0.7633082226454072</v>
       </c>
       <c r="D3">
         <v>1.478706220242042</v>
       </c>
       <c r="E3">
-        <v>0.93723344826192345</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.9372334482619235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1</v>
       </c>
@@ -516,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>0.84627276678653673</v>
+        <v>0.8462727667865367</v>
       </c>
       <c r="D4">
-        <v>1.7928481906966769</v>
+        <v>1.792848190696677</v>
       </c>
       <c r="E4">
         <v>1.118522846368402</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -533,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>4.5981480952944659E-2</v>
+        <v>0.04598148095294466</v>
       </c>
       <c r="D5">
-        <v>6.4151003259051126E-2</v>
+        <v>0.06415100325905113</v>
       </c>
       <c r="E5">
-        <v>0.39514869746584119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.3951486974658412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1</v>
       </c>
@@ -550,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>45.070924875713203</v>
+        <v>45.0709248757132</v>
       </c>
       <c r="D6">
-        <v>58.122659325516523</v>
+        <v>58.12265932551652</v>
       </c>
       <c r="E6">
-        <v>0.28958213051528342</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.2895821305152834</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1</v>
       </c>
@@ -567,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>38.439190811663259</v>
+        <v>38.43919081166326</v>
       </c>
       <c r="D7">
-        <v>59.222824437916572</v>
+        <v>59.22282443791657</v>
       </c>
       <c r="E7">
-        <v>0.54068863541079326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.5406886354107933</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1</v>
       </c>
@@ -587,13 +558,13 @@
         <v>168.5364152749716</v>
       </c>
       <c r="D8">
-        <v>71.630422852140981</v>
+        <v>71.63042285214098</v>
       </c>
       <c r="E8">
-        <v>0.57498548467834643</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.5749854846783464</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1</v>
       </c>
@@ -604,13 +575,13 @@
         <v>131.6720634196007</v>
       </c>
       <c r="D9">
-        <v>90.865908623414811</v>
+        <v>90.86590862341481</v>
       </c>
       <c r="E9">
         <v>0.3099074605229547</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1</v>
       </c>
@@ -618,16 +589,16 @@
         <v>13</v>
       </c>
       <c r="C10">
-        <v>61.099819770408288</v>
+        <v>61.09981977040829</v>
       </c>
       <c r="D10">
-        <v>13.617817447688219</v>
+        <v>13.61781744768822</v>
       </c>
       <c r="E10">
-        <v>0.77712180659682462</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.7771218065968246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1</v>
       </c>
@@ -635,16 +606,16 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>6.3613120923780624</v>
+        <v>6.361312092378062</v>
       </c>
       <c r="D11">
         <v>1.804689346183509</v>
       </c>
       <c r="E11">
-        <v>0.71630234140754789</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.7163023414075479</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1</v>
       </c>
@@ -652,16 +623,16 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>7.5312037308266611</v>
+        <v>7.531203730826661</v>
       </c>
       <c r="D12">
-        <v>6.4706125661439593</v>
+        <v>6.470612566143959</v>
       </c>
       <c r="E12">
         <v>0.1408262480460459</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1</v>
       </c>
@@ -669,16 +640,16 @@
         <v>16</v>
       </c>
       <c r="C13">
-        <v>0.82063317853748452</v>
+        <v>0.8206331785374845</v>
       </c>
       <c r="D13">
-        <v>0.73520676878183744</v>
+        <v>0.7352067687818374</v>
       </c>
       <c r="E13">
-        <v>0.10409816711029431</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.1040981671102943</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1</v>
       </c>
@@ -686,16 +657,16 @@
         <v>17</v>
       </c>
       <c r="C14">
-        <v>1.4540122227392329</v>
+        <v>1.454012222739233</v>
       </c>
       <c r="D14">
-        <v>0.75409970475784327</v>
+        <v>0.7540997047578433</v>
       </c>
       <c r="E14">
         <v>0.4813663234981721</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1750</v>
       </c>
@@ -703,16 +674,16 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>8.0663236164779467E-2</v>
+        <v>0.08066323616477947</v>
       </c>
       <c r="D15">
-        <v>1.7263832449837851E-2</v>
+        <v>0.01726383244983785</v>
       </c>
       <c r="E15">
-        <v>0.78597644638790398</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.785976446387904</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>1750</v>
       </c>
@@ -720,7 +691,7 @@
         <v>9</v>
       </c>
       <c r="C16">
-        <v>44.529166889689712</v>
+        <v>44.52916688968971</v>
       </c>
       <c r="D16">
         <v>26.20428771476346</v>
@@ -729,7 +700,7 @@
         <v>0.4115253092500411</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>1750</v>
       </c>
@@ -740,13 +711,13 @@
         <v>239.4481456879426</v>
       </c>
       <c r="D17">
-        <v>134.16739991140599</v>
+        <v>134.167399911406</v>
       </c>
       <c r="E17">
-        <v>0.43968077294589819</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.4396807729458982</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>1750</v>
       </c>
@@ -754,16 +725,16 @@
         <v>13</v>
       </c>
       <c r="C18">
-        <v>52.423224281098641</v>
+        <v>52.42322428109864</v>
       </c>
       <c r="D18">
-        <v>35.363591478016467</v>
+        <v>35.36359147801647</v>
       </c>
       <c r="E18">
-        <v>0.32542128106441309</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.3254212810644131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>1750</v>
       </c>
@@ -771,16 +742,16 @@
         <v>14</v>
       </c>
       <c r="C19">
-        <v>8.5655303097977722</v>
+        <v>8.565530309797772</v>
       </c>
       <c r="D19">
         <v>15.34784900745756</v>
       </c>
       <c r="E19">
-        <v>0.79181538706386512</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.7918153870638651</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>1750</v>
       </c>
@@ -788,16 +759,16 @@
         <v>15</v>
       </c>
       <c r="C20">
-        <v>7.2679714519001184</v>
+        <v>7.267971451900118</v>
       </c>
       <c r="D20">
-        <v>7.7699261499746468</v>
+        <v>7.769926149974647</v>
       </c>
       <c r="E20">
-        <v>6.9063933643176284E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.06906393364317628</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>1750</v>
       </c>
@@ -805,16 +776,16 @@
         <v>17</v>
       </c>
       <c r="C21">
-        <v>1.2427073120350089</v>
+        <v>1.242707312035009</v>
       </c>
       <c r="D21">
-        <v>0.83693094164153992</v>
+        <v>0.8369309416415399</v>
       </c>
       <c r="E21">
-        <v>0.32652609867482463</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.3265260986748246</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>1860</v>
       </c>
@@ -822,16 +793,16 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>5.7850326045561798E-2</v>
+        <v>0.0578503260455618</v>
       </c>
       <c r="D22">
-        <v>2.714234552061489E-2</v>
+        <v>0.02714234552061489</v>
       </c>
       <c r="E22">
         <v>0.5308177606598431</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>1860</v>
       </c>
@@ -839,16 +810,16 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>40.039388540877148</v>
+        <v>40.03938854087715</v>
       </c>
       <c r="D23">
-        <v>53.008632847819321</v>
+        <v>53.00863284781932</v>
       </c>
       <c r="E23">
         <v>0.323912147002484</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>1860</v>
       </c>
@@ -856,16 +827,16 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>36.030591578291741</v>
+        <v>36.03059157829174</v>
       </c>
       <c r="D24">
-        <v>60.118210661770753</v>
+        <v>60.11821066177075</v>
       </c>
       <c r="E24">
-        <v>0.66853243392183681</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.6685324339218368</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>1860</v>
       </c>
@@ -876,13 +847,13 @@
         <v>100.6177546971695</v>
       </c>
       <c r="D25">
-        <v>69.985749552839778</v>
+        <v>69.98574955283978</v>
       </c>
       <c r="E25">
-        <v>0.30443936297846519</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.3044393629784652</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>1860</v>
       </c>
@@ -890,16 +861,16 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>7.2287177192554131</v>
+        <v>7.228717719255413</v>
       </c>
       <c r="D26">
-        <v>7.3907584551274574</v>
+        <v>7.390758455127457</v>
       </c>
       <c r="E26">
-        <v>2.2416248934497781E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.02241624893449778</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>1860</v>
       </c>
@@ -907,16 +878,16 @@
         <v>16</v>
       </c>
       <c r="C27">
-        <v>0.96228384199408123</v>
+        <v>0.9622838419940812</v>
       </c>
       <c r="D27">
-        <v>0.99533209889304464</v>
+        <v>0.9953320988930446</v>
       </c>
       <c r="E27">
-        <v>3.4343564192535481E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.03434356419253548</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>1860</v>
       </c>
@@ -924,10 +895,10 @@
         <v>17</v>
       </c>
       <c r="C28">
-        <v>1.2015161595332611</v>
+        <v>1.201516159533261</v>
       </c>
       <c r="D28">
-        <v>0.92720470747569317</v>
+        <v>0.9272047074756932</v>
       </c>
       <c r="E28">
         <v>0.2283044217766714</v>
